--- a/procesos/inputs/mapeos_facturacion.xlsx
+++ b/procesos/inputs/mapeos_facturacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b8fc90e97c08fff/Nodus/Proyectos/Nodus-app/parche-gestoria/procesos/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_36D027D811D1424F995BE794A7388F960EB0E8F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE4A8869-8E6B-47FF-9A50-38D1C1A82F05}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_36D027D811D1424F995BE794A7388F960EB0E8F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5647441-88D0-4731-92CE-8F5DA0D7C1E8}"/>
   <bookViews>
-    <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14205" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ClientesXExptes" sheetId="4" r:id="rId1"/>
@@ -5551,25 +5551,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="4" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="4" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -5615,12 +5597,6 @@
     <xf numFmtId="2" fontId="8" fillId="4" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5632,52 +5608,7 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="6" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5746,6 +5677,51 @@
     <xf numFmtId="2" fontId="16" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="16" fillId="6" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="16" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5755,11 +5731,35 @@
     <xf numFmtId="2" fontId="16" fillId="6" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="6" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6041,6 +6041,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6309,6 +6313,9 @@
   </sheetPr>
   <dimension ref="A1:B854"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="12.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -26387,64 +26394,64 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.54296875" style="30" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" style="30" customWidth="1"/>
-    <col min="3" max="3" width="18" style="30" customWidth="1"/>
-    <col min="4" max="16384" width="11.453125" style="30"/>
+    <col min="1" max="1" width="19.54296875" style="27" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" style="27" customWidth="1"/>
+    <col min="3" max="3" width="18" style="27" customWidth="1"/>
+    <col min="4" max="16384" width="11.453125" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="73" t="s">
         <v>1537</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
     </row>
     <row r="2" spans="1:3" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="76" t="s">
         <v>1538</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="33"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="78"/>
     </row>
     <row r="3" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="28" t="s">
         <v>1539</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="29" t="s">
         <v>1540</v>
       </c>
-      <c r="C3" s="35"/>
+      <c r="C3" s="29"/>
     </row>
     <row r="4" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
     </row>
     <row r="5" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
     </row>
     <row r="6" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
     </row>
     <row r="7" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
     </row>
     <row r="9" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -26464,104 +26471,104 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" style="30" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" style="30" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="30" customWidth="1"/>
-    <col min="4" max="16384" width="11.453125" style="30"/>
+    <col min="1" max="1" width="28" style="27" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" style="27" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" style="27" customWidth="1"/>
+    <col min="4" max="16384" width="11.453125" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="73" t="s">
         <v>1541</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="37"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="28" t="s">
         <v>1542</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="32" t="s">
         <v>1543</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="33" t="s">
         <v>1544</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="34" t="s">
         <v>1545</v>
       </c>
-      <c r="B3" s="41">
+      <c r="B3" s="35">
         <v>56</v>
       </c>
-      <c r="C3" s="42">
+      <c r="C3" s="36">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="34" t="s">
         <v>1546</v>
       </c>
-      <c r="B4" s="43">
+      <c r="B4" s="37">
         <v>56</v>
       </c>
-      <c r="C4" s="44">
+      <c r="C4" s="38">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="34" t="s">
         <v>1547</v>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="37">
         <v>83</v>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="38">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="34" t="s">
         <v>1548</v>
       </c>
-      <c r="B6" s="43">
+      <c r="B6" s="37">
         <v>123</v>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="38">
         <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="34" t="s">
         <v>1549</v>
       </c>
-      <c r="B7" s="43">
+      <c r="B7" s="37">
         <v>166</v>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="38">
         <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="34" t="s">
         <v>1550</v>
       </c>
-      <c r="B8" s="43">
+      <c r="B8" s="37">
         <v>248</v>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="38">
         <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="34" t="s">
         <v>1551</v>
       </c>
-      <c r="B9" s="45">
+      <c r="B9" s="39">
         <v>331</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="40">
         <v>298</v>
       </c>
     </row>
@@ -26582,128 +26589,128 @@
   <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.26953125" style="30" customWidth="1"/>
-    <col min="2" max="16384" width="11.453125" style="30"/>
+    <col min="1" max="1" width="33.26953125" style="27" customWidth="1"/>
+    <col min="2" max="16384" width="11.453125" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="41" t="s">
         <v>1552</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="42"/>
     </row>
     <row r="2" spans="1:2" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="79" t="s">
         <v>1553</v>
       </c>
-      <c r="B2" s="50"/>
+      <c r="B2" s="80"/>
     </row>
     <row r="3" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="43" t="s">
         <v>1554</v>
       </c>
-      <c r="B3" s="52">
+      <c r="B3" s="44">
         <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="43" t="s">
         <v>1555</v>
       </c>
-      <c r="B4" s="52">
+      <c r="B4" s="44">
         <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="43" t="s">
         <v>1556</v>
       </c>
-      <c r="B5" s="52">
+      <c r="B5" s="44">
         <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="43" t="s">
         <v>1557</v>
       </c>
-      <c r="B6" s="52">
+      <c r="B6" s="44">
         <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="43" t="s">
         <v>1558</v>
       </c>
-      <c r="B7" s="52">
+      <c r="B7" s="44">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="43" t="s">
         <v>1559</v>
       </c>
-      <c r="B8" s="52">
+      <c r="B8" s="44">
         <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="43" t="s">
         <v>1560</v>
       </c>
-      <c r="B9" s="52">
+      <c r="B9" s="44">
         <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="43" t="s">
         <v>1561</v>
       </c>
-      <c r="B10" s="52">
+      <c r="B10" s="44">
         <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="43" t="s">
         <v>1562</v>
       </c>
-      <c r="B11" s="52">
+      <c r="B11" s="44">
         <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="43" t="s">
         <v>1563</v>
       </c>
-      <c r="B12" s="52">
+      <c r="B12" s="44">
         <v>367</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
+      <c r="B15" s="45"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
+      <c r="B16" s="45"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="53"/>
+      <c r="B17" s="45"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="53"/>
+      <c r="B18" s="45"/>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="53"/>
+      <c r="B19" s="45"/>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="53"/>
+      <c r="B20" s="45"/>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="53"/>
+      <c r="B21" s="45"/>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="53"/>
+      <c r="B22" s="45"/>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="53"/>
+      <c r="B23" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -26722,536 +26729,531 @@
   <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" style="98" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.81640625" style="30" customWidth="1"/>
-    <col min="3" max="3" width="7.7265625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.81640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="30" customWidth="1"/>
-    <col min="6" max="7" width="7.7265625" style="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="30" customWidth="1"/>
-    <col min="9" max="16384" width="11.453125" style="30"/>
+    <col min="1" max="1" width="19.7265625" style="72" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.81640625" style="27" customWidth="1"/>
+    <col min="3" max="3" width="7.7265625" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="27" customWidth="1"/>
+    <col min="6" max="7" width="7.7265625" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="27" customWidth="1"/>
+    <col min="9" max="16384" width="11.453125" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="73" t="s">
         <v>1564</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="56" t="s">
+      <c r="A2" s="46"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="89" t="s">
         <v>1565</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="59" t="s">
+      <c r="D2" s="90"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92" t="s">
         <v>1566</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="61"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="94"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="83" t="s">
         <v>1567</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="64"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="85"/>
     </row>
     <row r="4" spans="1:12" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="95" t="s">
         <v>1568</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66" t="s">
+      <c r="B4" s="97"/>
+      <c r="C4" s="97" t="s">
         <v>1569</v>
       </c>
-      <c r="D4" s="66" t="s">
+      <c r="D4" s="97" t="s">
         <v>1570</v>
       </c>
-      <c r="E4" s="66" t="s">
+      <c r="E4" s="97" t="s">
         <v>1571</v>
       </c>
-      <c r="F4" s="67" t="s">
+      <c r="F4" s="81" t="s">
         <v>1569</v>
       </c>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="81" t="s">
         <v>1572</v>
       </c>
-      <c r="H4" s="68" t="s">
+      <c r="H4" s="48" t="s">
         <v>1573</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="69"/>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="72" t="s">
+      <c r="A5" s="96"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="49" t="s">
         <v>1574</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="50" t="s">
         <v>1575</v>
       </c>
-      <c r="B6" s="74"/>
-      <c r="C6" s="75">
+      <c r="B6" s="51"/>
+      <c r="C6" s="52">
         <v>45</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="52">
         <v>18</v>
       </c>
-      <c r="E6" s="75">
+      <c r="E6" s="52">
         <f>C6+D6</f>
         <v>63</v>
       </c>
-      <c r="F6" s="76">
+      <c r="F6" s="53">
         <v>85</v>
       </c>
-      <c r="G6" s="76">
+      <c r="G6" s="53">
         <v>18</v>
       </c>
-      <c r="H6" s="76">
+      <c r="H6" s="53">
         <f>F6+G6</f>
         <v>103</v>
       </c>
-      <c r="L6" s="53"/>
+      <c r="L6" s="45"/>
     </row>
     <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="50" t="s">
         <v>1576</v>
       </c>
-      <c r="B7" s="74"/>
-      <c r="C7" s="75">
+      <c r="B7" s="51"/>
+      <c r="C7" s="52">
         <v>54</v>
       </c>
-      <c r="D7" s="75">
+      <c r="D7" s="52">
         <v>18</v>
       </c>
-      <c r="E7" s="75">
+      <c r="E7" s="52">
         <f t="shared" ref="E7:E10" si="0">C7+D7</f>
         <v>72</v>
       </c>
-      <c r="F7" s="76">
+      <c r="F7" s="53">
         <v>90</v>
       </c>
-      <c r="G7" s="76">
+      <c r="G7" s="53">
         <v>18</v>
       </c>
-      <c r="H7" s="76">
+      <c r="H7" s="53">
         <f>F7+G7</f>
         <v>108</v>
       </c>
-      <c r="L7" s="53"/>
+      <c r="L7" s="45"/>
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="50" t="s">
         <v>1577</v>
       </c>
-      <c r="B8" s="74"/>
-      <c r="C8" s="75">
+      <c r="B8" s="51"/>
+      <c r="C8" s="52">
         <v>58</v>
       </c>
-      <c r="D8" s="75">
+      <c r="D8" s="52">
         <v>28</v>
       </c>
-      <c r="E8" s="75">
+      <c r="E8" s="52">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="F8" s="76">
+      <c r="F8" s="53">
         <v>97</v>
       </c>
-      <c r="G8" s="76">
+      <c r="G8" s="53">
         <v>28</v>
       </c>
-      <c r="H8" s="76">
+      <c r="H8" s="53">
         <f>F8+G8</f>
         <v>125</v>
       </c>
-      <c r="L8" s="53"/>
+      <c r="L8" s="45"/>
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="50" t="s">
         <v>1578</v>
       </c>
-      <c r="B9" s="74"/>
-      <c r="C9" s="75">
+      <c r="B9" s="51"/>
+      <c r="C9" s="52">
         <v>64</v>
       </c>
-      <c r="D9" s="75">
+      <c r="D9" s="52">
         <v>28</v>
       </c>
-      <c r="E9" s="75">
+      <c r="E9" s="52">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="F9" s="76">
+      <c r="F9" s="53">
         <v>103</v>
       </c>
-      <c r="G9" s="76">
+      <c r="G9" s="53">
         <v>28</v>
       </c>
-      <c r="H9" s="76">
+      <c r="H9" s="53">
         <f>F9+G9</f>
         <v>131</v>
       </c>
-      <c r="L9" s="53"/>
+      <c r="L9" s="45"/>
     </row>
     <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="50" t="s">
         <v>1579</v>
       </c>
-      <c r="B10" s="74"/>
-      <c r="C10" s="75">
+      <c r="B10" s="51"/>
+      <c r="C10" s="52">
         <v>68</v>
       </c>
-      <c r="D10" s="75">
+      <c r="D10" s="52">
         <v>28</v>
       </c>
-      <c r="E10" s="75">
+      <c r="E10" s="52">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="F10" s="76">
+      <c r="F10" s="53">
         <v>109</v>
       </c>
-      <c r="G10" s="76">
+      <c r="G10" s="53">
         <v>28</v>
       </c>
-      <c r="H10" s="76">
+      <c r="H10" s="53">
         <f>F10+G10</f>
         <v>137</v>
       </c>
-      <c r="L10" s="53"/>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
+      <c r="A11" s="50"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
     </row>
     <row r="12" spans="1:12" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="83" t="s">
         <v>1580</v>
       </c>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="64"/>
+      <c r="B12" s="84"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="85"/>
     </row>
     <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="56" t="s">
         <v>1581</v>
       </c>
-      <c r="B13" s="80"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
     </row>
     <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="82">
+      <c r="A14" s="59">
         <v>-10000</v>
       </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="84">
+      <c r="B14" s="60"/>
+      <c r="C14" s="61">
         <v>34</v>
       </c>
-      <c r="D14" s="84">
+      <c r="D14" s="61">
         <v>15</v>
       </c>
-      <c r="E14" s="84">
+      <c r="E14" s="61">
         <f>C14+D14</f>
         <v>49</v>
       </c>
-      <c r="F14" s="85">
+      <c r="F14" s="62">
         <v>54</v>
       </c>
-      <c r="G14" s="85">
+      <c r="G14" s="62">
         <v>15</v>
       </c>
-      <c r="H14" s="85">
+      <c r="H14" s="62">
         <f>F14+G14</f>
         <v>69</v>
       </c>
-      <c r="J14" s="53"/>
-      <c r="K14" s="86"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="63"/>
     </row>
     <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="64" t="s">
         <v>1576</v>
       </c>
-      <c r="B15" s="83"/>
-      <c r="C15" s="84">
+      <c r="B15" s="60"/>
+      <c r="C15" s="61">
         <v>36</v>
       </c>
-      <c r="D15" s="84">
+      <c r="D15" s="61">
         <v>15</v>
       </c>
-      <c r="E15" s="84">
+      <c r="E15" s="61">
         <f t="shared" ref="E15:E18" si="1">C15+D15</f>
         <v>51</v>
       </c>
-      <c r="F15" s="85">
+      <c r="F15" s="62">
         <v>66</v>
       </c>
-      <c r="G15" s="85">
+      <c r="G15" s="62">
         <v>15</v>
       </c>
-      <c r="H15" s="85">
+      <c r="H15" s="62">
         <f>F15+G15</f>
         <v>81</v>
       </c>
-      <c r="J15" s="53"/>
-      <c r="K15" s="86"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="63"/>
     </row>
     <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="87" t="s">
+      <c r="A16" s="64" t="s">
         <v>1577</v>
       </c>
-      <c r="B16" s="83"/>
-      <c r="C16" s="84">
+      <c r="B16" s="60"/>
+      <c r="C16" s="61">
         <v>40</v>
       </c>
-      <c r="D16" s="84">
+      <c r="D16" s="61">
         <v>21</v>
       </c>
-      <c r="E16" s="84">
+      <c r="E16" s="61">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="F16" s="85">
+      <c r="F16" s="62">
         <v>69</v>
       </c>
-      <c r="G16" s="85">
+      <c r="G16" s="62">
         <v>21</v>
       </c>
-      <c r="H16" s="85">
+      <c r="H16" s="62">
         <f>F16+G16</f>
         <v>90</v>
       </c>
-      <c r="J16" s="53"/>
-      <c r="K16" s="86"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="63"/>
     </row>
     <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="87" t="s">
+      <c r="A17" s="64" t="s">
         <v>1578</v>
       </c>
-      <c r="B17" s="83"/>
-      <c r="C17" s="84">
+      <c r="B17" s="60"/>
+      <c r="C17" s="61">
         <v>43</v>
       </c>
-      <c r="D17" s="84">
+      <c r="D17" s="61">
         <v>21</v>
       </c>
-      <c r="E17" s="84">
+      <c r="E17" s="61">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="F17" s="85">
+      <c r="F17" s="62">
         <v>75</v>
       </c>
-      <c r="G17" s="85">
+      <c r="G17" s="62">
         <v>21</v>
       </c>
-      <c r="H17" s="85">
+      <c r="H17" s="62">
         <f>F17+G17</f>
         <v>96</v>
       </c>
-      <c r="J17" s="53"/>
-      <c r="K17" s="86"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="63"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="87" t="s">
+      <c r="A18" s="64" t="s">
         <v>1579</v>
       </c>
-      <c r="B18" s="83"/>
-      <c r="C18" s="84">
+      <c r="B18" s="60"/>
+      <c r="C18" s="61">
         <v>48</v>
       </c>
-      <c r="D18" s="84">
+      <c r="D18" s="61">
         <v>21</v>
       </c>
-      <c r="E18" s="84">
+      <c r="E18" s="61">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="F18" s="85">
+      <c r="F18" s="62">
         <v>78</v>
       </c>
-      <c r="G18" s="85">
+      <c r="G18" s="62">
         <v>21</v>
       </c>
-      <c r="H18" s="85">
+      <c r="H18" s="62">
         <f>F18+G18</f>
         <v>99</v>
       </c>
-      <c r="J18" s="53"/>
-      <c r="K18" s="86"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="63"/>
     </row>
     <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="73"/>
-      <c r="B19" s="74"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
+      <c r="A19" s="50"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:11" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="62" t="s">
+      <c r="A20" s="83" t="s">
         <v>1582</v>
       </c>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="64"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="84"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="85"/>
     </row>
     <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="88" t="s">
+      <c r="A21" s="65" t="s">
         <v>1583</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="90"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="68" t="s">
         <v>1584</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="93">
+      <c r="B22" s="69"/>
+      <c r="C22" s="70">
         <v>0</v>
       </c>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93">
+      <c r="D22" s="70"/>
+      <c r="E22" s="70">
         <v>0</v>
       </c>
-      <c r="F22" s="94" t="s">
+      <c r="F22" s="86" t="s">
         <v>1585</v>
       </c>
-      <c r="G22" s="95"/>
-      <c r="H22" s="96"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="88"/>
     </row>
     <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="91" t="s">
+      <c r="A23" s="68" t="s">
         <v>1586</v>
       </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="93">
+      <c r="B23" s="69"/>
+      <c r="C23" s="70">
         <v>21</v>
       </c>
-      <c r="D23" s="93">
+      <c r="D23" s="70">
         <v>18</v>
       </c>
-      <c r="E23" s="93">
+      <c r="E23" s="70">
         <f>C23+D23</f>
         <v>39</v>
       </c>
-      <c r="F23" s="94" t="s">
+      <c r="F23" s="86" t="s">
         <v>1587</v>
       </c>
-      <c r="G23" s="95"/>
-      <c r="H23" s="96"/>
+      <c r="G23" s="87"/>
+      <c r="H23" s="88"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="91" t="s">
+      <c r="A24" s="68" t="s">
         <v>1588</v>
       </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="93">
+      <c r="B24" s="69"/>
+      <c r="C24" s="70">
         <v>32</v>
       </c>
-      <c r="D24" s="93">
+      <c r="D24" s="70">
         <v>18</v>
       </c>
-      <c r="E24" s="93">
+      <c r="E24" s="70">
         <f t="shared" ref="E24:E26" si="2">C24+D24</f>
         <v>50</v>
       </c>
-      <c r="F24" s="97"/>
-      <c r="G24" s="97"/>
-      <c r="H24" s="97"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
     </row>
     <row r="25" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="91" t="s">
+      <c r="A25" s="68" t="s">
         <v>1589</v>
       </c>
-      <c r="B25" s="92"/>
-      <c r="C25" s="93">
+      <c r="B25" s="69"/>
+      <c r="C25" s="70">
         <v>42</v>
       </c>
-      <c r="D25" s="93">
+      <c r="D25" s="70">
         <v>18</v>
       </c>
-      <c r="E25" s="93">
+      <c r="E25" s="70">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="F25" s="97"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="97"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="91" t="s">
+      <c r="A26" s="68" t="s">
         <v>1590</v>
       </c>
-      <c r="B26" s="92"/>
-      <c r="C26" s="93">
+      <c r="B26" s="69"/>
+      <c r="C26" s="70">
         <v>55</v>
       </c>
-      <c r="D26" s="93">
+      <c r="D26" s="70">
         <v>18</v>
       </c>
-      <c r="E26" s="93">
+      <c r="E26" s="70">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="F26" s="97"/>
-      <c r="G26" s="97"/>
-      <c r="H26" s="97"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:H2"/>
@@ -27262,6 +27264,11 @@
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
